--- a/Python/dz2/work/output/animals_age_range.xlsx
+++ b/Python/dz2/work/output/animals_age_range.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="25">
   <si>
     <t>name</t>
   </si>
@@ -37,13 +37,58 @@
     <t>Муся</t>
   </si>
   <si>
+    <t>Барсик</t>
+  </si>
+  <si>
+    <t>Ася</t>
+  </si>
+  <si>
+    <t>Нора</t>
+  </si>
+  <si>
+    <t>Чарли</t>
+  </si>
+  <si>
+    <t>Рыжик</t>
+  </si>
+  <si>
+    <t>Мила</t>
+  </si>
+  <si>
+    <t>Бакс</t>
+  </si>
+  <si>
+    <t>Снежок</t>
+  </si>
+  <si>
+    <t>Дина</t>
+  </si>
+  <si>
+    <t>Лея</t>
+  </si>
+  <si>
     <t>Кошка</t>
   </si>
   <si>
+    <t>Собака</t>
+  </si>
+  <si>
     <t>Персидская</t>
   </si>
   <si>
+    <t>Британская короткошерстная</t>
+  </si>
+  <si>
+    <t>Мейн-кун</t>
+  </si>
+  <si>
+    <t>Овчарка</t>
+  </si>
+  <si>
     <t>В приюте</t>
+  </si>
+  <si>
+    <t>На лечении</t>
   </si>
 </sst>
 </file>
@@ -401,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -429,10 +474,10 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -441,7 +486,195 @@
         <v>119</v>
       </c>
       <c r="F2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>3.7</v>
+      </c>
+      <c r="E3">
+        <v>70</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4">
+        <v>4.4</v>
+      </c>
+      <c r="E4">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>3.7</v>
+      </c>
+      <c r="E5">
+        <v>62</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6">
+        <v>4.8</v>
+      </c>
+      <c r="E6">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>2.3</v>
+      </c>
+      <c r="E7">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8">
+        <v>2.5</v>
+      </c>
+      <c r="E8">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>4.8</v>
+      </c>
+      <c r="E9">
+        <v>72</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10">
+        <v>2.4</v>
+      </c>
+      <c r="E10">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11">
+        <v>4.5</v>
+      </c>
+      <c r="E11">
+        <v>66</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12">
+        <v>2.9</v>
+      </c>
+      <c r="E12">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
